--- a/artfynd/A 12432-2024 artfynd.xlsx
+++ b/artfynd/A 12432-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117504264</v>
+        <v>117504985</v>
       </c>
       <c r="B7" t="n">
-        <v>57930</v>
+        <v>57963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,20 +1299,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117504985</v>
+        <v>117504264</v>
       </c>
       <c r="B8" t="n">
-        <v>57963</v>
+        <v>57930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,20 +1420,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12432-2024 artfynd.xlsx
+++ b/artfynd/A 12432-2024 artfynd.xlsx
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117504299</v>
+        <v>117503905</v>
       </c>
       <c r="B4" t="n">
-        <v>56933</v>
+        <v>57656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,32 +936,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102964</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -969,14 +965,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sånghusvallen, Tysjöarnas naturreservat, Jmt</t>
+          <t>Sånghusvallen E14, Tysjöarnas naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479924</v>
+        <v>480343</v>
       </c>
       <c r="R4" t="n">
-        <v>7010921</v>
+        <v>7011258</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117504259</v>
+        <v>117504985</v>
       </c>
       <c r="B5" t="n">
-        <v>57721</v>
+        <v>57963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,30 +1053,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1129,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117504367</v>
+        <v>117504299</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>56933</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,16 +1178,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>102964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117504985</v>
+        <v>117504367</v>
       </c>
       <c r="B7" t="n">
-        <v>57963</v>
+        <v>57990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,25 +1295,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1327,7 +1323,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1371,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117504264</v>
+        <v>117504396</v>
       </c>
       <c r="B8" t="n">
-        <v>57930</v>
+        <v>57715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,25 +1416,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1448,7 +1444,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1492,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1498,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117504396</v>
+        <v>117504264</v>
       </c>
       <c r="B9" t="n">
-        <v>57715</v>
+        <v>57930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,25 +1537,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1613,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1623,7 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117503905</v>
+        <v>117504259</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57721</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,43 +1658,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sånghusvallen E14, Tysjöarnas naturreservat, Jmt</t>
+          <t>Sånghusvallen, Tysjöarnas naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480343</v>
+        <v>479924</v>
       </c>
       <c r="R10" t="n">
-        <v>7011258</v>
+        <v>7010921</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 12432-2024 artfynd.xlsx
+++ b/artfynd/A 12432-2024 artfynd.xlsx
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117503905</v>
+        <v>117504259</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,43 +936,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sånghusvallen E14, Tysjöarnas naturreservat, Jmt</t>
+          <t>Sånghusvallen, Tysjöarnas naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480343</v>
+        <v>479924</v>
       </c>
       <c r="R4" t="n">
-        <v>7011258</v>
+        <v>7010921</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1004,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117504985</v>
+        <v>117504299</v>
       </c>
       <c r="B5" t="n">
-        <v>57963</v>
+        <v>56934</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,25 +1057,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1081,7 +1085,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1125,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117504299</v>
+        <v>117504367</v>
       </c>
       <c r="B6" t="n">
-        <v>56933</v>
+        <v>57991</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,16 +1182,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102964</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117504367</v>
+        <v>117503905</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>57657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,47 +1299,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sånghusvallen, Tysjöarnas naturreservat, Jmt</t>
+          <t>Sånghusvallen E14, Tysjöarnas naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479924</v>
+        <v>480343</v>
       </c>
       <c r="R7" t="n">
-        <v>7010921</v>
+        <v>7011258</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117504396</v>
+        <v>117504264</v>
       </c>
       <c r="B8" t="n">
-        <v>57715</v>
+        <v>57931</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117504264</v>
+        <v>117504396</v>
       </c>
       <c r="B9" t="n">
-        <v>57930</v>
+        <v>57716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117504259</v>
+        <v>117504985</v>
       </c>
       <c r="B10" t="n">
-        <v>57721</v>
+        <v>57964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,30 +1658,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>06:24</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
